--- a/artfynd/A 34414-2026 artfynd.xlsx
+++ b/artfynd/A 34414-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293901</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136293898</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293899</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
